--- a/strategic_plans/02_import_and_clean_qual_codes/code_crosswalk.xlsx
+++ b/strategic_plans/02_import_and_clean_qual_codes/code_crosswalk.xlsx
@@ -1198,7 +1198,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Parents and Community</t>
+          <t>Family and Community</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
